--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>90893</v>
+        <v>90985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>90985</v>
+        <v>90991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>90991</v>
+        <v>90997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>90997</v>
+        <v>90999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>90999</v>
+        <v>91000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91000</v>
+        <v>91027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91027</v>
+        <v>91032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>91037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91037</v>
+        <v>91041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91041</v>
+        <v>91046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91048</v>
+        <v>91072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91072</v>
+        <v>91073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91073</v>
+        <v>91076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91076</v>
+        <v>91078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91078</v>
+        <v>91082</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91083</v>
+        <v>91086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91086</v>
+        <v>91114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91114</v>
+        <v>91120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91120</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91126</v>
+        <v>91130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24368-2025 artfynd.xlsx
+++ b/artfynd/A 24368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128478102</v>
       </c>
       <c r="B2" t="n">
-        <v>91130</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
